--- a/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
+++ b/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'任务清单'!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'任务清单'!$A$1:$K$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -297,12 +297,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'甘特图-图表'!$B$2:$B$39</f>
+              <f>'甘特图-图表'!$B$2:$B$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'甘特图-图表'!$D$2:$D$39</f>
+              <f>'甘特图-图表'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'甘特图-图表'!$B$2:$B$39</f>
+              <f>'甘特图-图表'!$B$2:$B$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'甘特图-图表'!$E$2:$E$39</f>
+              <f>'甘特图-图表'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>需求调研与竞品分析</t>
+          <t>调研方案与问卷设计</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>调研记录、竞品分析表</t>
+          <t>调研方案、问卷与访谈提纲</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>可行性分析报告</t>
+          <t>问卷发放与回收（≥200 份）</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.35</v>
+        <v>0.75</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>T1.4</t>
+          <t>T2.1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>可行性分析报告（10/21）</t>
+          <t>问卷原始数据</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1265,40 +1265,40 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>T3.1</t>
+          <t>T2.3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>需求获取与建模（用例/数据流）</t>
+          <t>竞品分析与群内供需观察</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>WP3</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>需求分析</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>T2.2</t>
+          <t>T2.1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1308,47 +1308,47 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>用例图、数据流图</t>
+          <t>竞品对比表、群内观察记录</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T3.2</t>
+          <t>T2.4</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>需求规格说明书 SRS</t>
+          <t>调研数据整理与统计</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>WP3</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>需求分析</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1358,112 +1358,112 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>SRS（10/28）</t>
+          <t>调研数据小结</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T3.3</t>
+          <t>T2.5</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>需求评审 PPT 与答辩</t>
+          <t>技术可行性验证（云开发原型）</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>WP3</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>需求分析</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>T3.2</t>
+          <t>T1.4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>需求评审PPT</t>
+          <t>技术验证结论与原型截图</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T3.4</t>
+          <t>T2.6</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SRS 修订</t>
+          <t>成本与效益测算</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>WP3</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>需求分析</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>T3.3</t>
+          <t>T1.4</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1473,52 +1473,52 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>SRS 修订版（11/4）</t>
+          <t>成本测算表、收益/投资比测算</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T4.1</t>
+          <t>T2.7</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>总体设计报告</t>
+          <t>合规与主体资质核查</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WP4</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>总体设计</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>T3.4</t>
+          <t>T1.4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1528,199 +1528,199 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>总体设计报告（11/11）</t>
+          <t>合规核查记录、资质路径结论</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T4.2</t>
+          <t>T2.8</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>交互原型与 UI 视觉设计</t>
+          <t>可行性分析报告撰写（GB 8567）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WP4</t>
+          <t>WP2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>总体设计</t>
+          <t>可行性研究</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>T3.4</t>
+          <t>T2.4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>原型稿、UI 视觉稿</t>
+          <t>可行性分析报告（10/21）</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T4.3</t>
+          <t>T3.1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>数据库与接口设计</t>
+          <t>需求获取与建模（用例/数据流）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WP4</t>
+          <t>WP3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>总体设计</t>
+          <t>需求分析</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>T4.1</t>
+          <t>T2.8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>数据库与接口文档</t>
+          <t>用例图、数据流图</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T5.1</t>
+          <t>T3.2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>详细设计报告</t>
+          <t>需求规格说明书 SRS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WP5</t>
+          <t>WP3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>详细设计</t>
+          <t>需求分析</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>T4.1</t>
+          <t>T2.8</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>详细设计报告（11/18）</t>
+          <t>SRS（10/28）</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T3.3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>设计评审 PPT（翻转 PPT1）</t>
+          <t>需求评审 PPT 与答辩</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WP5</t>
+          <t>WP3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>详细设计</t>
+          <t>需求分析</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>T5.1</t>
+          <t>T3.2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1748,34 +1748,34 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>设计评审PPT（11/25）</t>
+          <t>需求评审PPT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T5.3</t>
+          <t>T3.4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>设计修订与接口冻结</t>
+          <t>SRS 修订</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WP5</t>
+          <t>WP3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>详细设计</t>
+          <t>需求分析</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T3.3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1803,89 +1803,89 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>设计修订说明</t>
+          <t>SRS 修订版（11/4）</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>T6.1</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>框架搭建与登录认证</t>
+          <t>总体设计报告</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>总体设计</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>T5.3</t>
+          <t>T3.4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>认证模块</t>
+          <t>总体设计报告（11/11）</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T6.2</t>
+          <t>T4.2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>快递代取模块开发</t>
+          <t>交互原型与 UI 视觉设计</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP4</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>总体设计</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>T6.1</t>
+          <t>T3.4</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1913,34 +1913,34 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>代取模块</t>
+          <t>原型稿、UI 视觉稿</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T6.3</t>
+          <t>T4.3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>二手教材模块开发</t>
+          <t>数据库与接口设计</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>总体设计</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1948,58 +1948,58 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>T6.1</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>教材模块</t>
+          <t>数据库与接口文档</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T6.4</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>云函数与数据库实现</t>
+          <t>详细设计报告</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP5</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>详细设计</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -2013,17 +2013,17 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>T5.3</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>云函数与数据集合</t>
+          <t>详细设计报告（11/18）</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2035,26 +2035,26 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>T6.5</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>积分账本与风控规则</t>
+          <t>设计评审 PPT（翻转 PPT1）</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>详细设计</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2063,49 +2063,49 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>T6.4</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>积分账本模块</t>
+          <t>设计评审PPT（11/25）</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T6.6</t>
+          <t>T5.3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>信用评价与申诉模块</t>
+          <t>设计修订与接口冻结</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>WP6</t>
+          <t>WP5</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>编码实现</t>
+          <t>详细设计</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>T6.5</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>评价与申诉模块</t>
+          <t>设计修订说明</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>T6.7</t>
+          <t>T6.1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>地图与消息推送对接</t>
+          <t>框架搭建与登录认证</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>T6.2</t>
+          <t>T5.3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>地图与推送模块</t>
+          <t>认证模块</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T6.8</t>
+          <t>T6.2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>集成联调与代码清单（翻转PPT2）</t>
+          <t>快递代取模块开发</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2219,76 +2219,76 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>T6.3,T6.5,T6.6,T6.7</t>
+          <t>T6.1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>代码清单（12/2）</t>
+          <t>代取模块</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T6.3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>测试用例设计</t>
+          <t>二手教材模块开发</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>WP7</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>T6.8</t>
+          <t>T6.1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2298,107 +2298,107 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>测试用例集</t>
+          <t>教材模块</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T6.4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>功能与边界测试</t>
+          <t>云函数与数据库实现</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>WP7</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T5.3</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>缺陷台账</t>
+          <t>云函数与数据集合</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T7.3</t>
+          <t>T6.5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>并发与积分一致性测试</t>
+          <t>积分账本与风控规则</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>WP7</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>T6.8</t>
+          <t>T6.4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2408,34 +2408,34 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>一致性测试报告</t>
+          <t>积分账本模块</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T7.4</t>
+          <t>T6.6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>系统测试报告</t>
+          <t>信用评价与申诉模块</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>WP7</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
@@ -2443,54 +2443,54 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>T7.2,T7.3</t>
+          <t>T6.5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>系统测试报告（12/9）</t>
+          <t>评价与申诉模块</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T7.5</t>
+          <t>T6.7</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>测试评审与缺陷修复</t>
+          <t>地图与消息推送对接</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>WP7</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -2498,123 +2498,127 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>T7.4</t>
+          <t>T6.2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>测试报告修订（12/16）</t>
+          <t>地图与推送模块</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T8.1</t>
+          <t>T6.8</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>性能与体验优化</t>
+          <t>集成联调与代码清单（翻转PPT2）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>WP8</t>
+          <t>WP6</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>维护</t>
+          <t>编码实现</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>T7.5</t>
+          <t>T6.3,T6.5,T6.6,T6.7</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>优化记录</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+          <t>代码清单（12/2）</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>T8.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>单校区试运行与用户反馈</t>
+          <t>测试用例设计</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>WP8</t>
+          <t>WP7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>维护</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>T7.5</t>
+          <t>T6.8</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2624,48 +2628,52 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>试点数据与反馈</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>测试用例集</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T8.3</t>
+          <t>T7.2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>用户使用手册编写</t>
+          <t>功能与边界测试</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>WP8</t>
+          <t>WP7</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>维护</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>T7.4</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2675,48 +2683,52 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>用户使用手册</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
+          <t>缺陷台账</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>T9.1</t>
+          <t>T7.3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>项目总结报告</t>
+          <t>并发与积分一致性测试</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>WP9</t>
+          <t>WP7</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>总结验收</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>T8.2</t>
+          <t>T6.8</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2726,89 +2738,89 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>项目总结报告（12/30）</t>
+          <t>一致性测试报告</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>M12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>T9.2</t>
+          <t>T7.4</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>总评审 PPT 与答辩</t>
+          <t>系统测试报告</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>WP9</t>
+          <t>WP7</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>总结验收</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>T9.1</t>
+          <t>T7.2,T7.3</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>总评审PPT</t>
+          <t>系统测试报告（12/9）</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>M12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>T9.3</t>
+          <t>T7.5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>课程作业评审与资料归档</t>
+          <t>测试评审与缺陷修复</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>WP9</t>
+          <t>WP7</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>总结验收</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
@@ -2816,37 +2828,355 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>T7.4</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>测试报告修订（12/16）</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>T8.1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>性能与体验优化</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>WP8</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>T7.5</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>优化记录</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>T8.2</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>单校区试运行与用户反馈</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>WP8</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>T7.5</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>试点数据与反馈</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>T8.3</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>用户使用手册编写</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>WP8</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>T7.4</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>用户使用手册</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>T9.1</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>项目总结报告</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>WP9</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>总结验收</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>T8.2</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>项目总结报告（12/30）</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>T9.2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>总评审 PPT 与答辩</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>WP9</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>总结验收</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>T9.1</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>总评审PPT</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>T9.3</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>课程作业评审与资料归档</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>WP9</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>总结验收</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>T9.2</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>归档材料（1/6）</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2857,7 +3187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3244,7 +3574,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>需求调研与竞品分析</t>
+          <t>调研方案与问卷设计</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3253,13 +3583,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
@@ -3280,22 +3610,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>可行性分析报告</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>问卷发放与回收（≥200 份）</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3.35</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
@@ -3311,12 +3641,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>T3.1</t>
+          <t>T2.3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>需求获取与建模（用例/数据流）</t>
+          <t>竞品分析与群内供需观察</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -3325,15 +3655,15 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr"/>
@@ -3347,29 +3677,29 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T3.2</t>
+          <t>T2.4</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>需求规格说明书 SRS</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>调研数据整理与统计</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr"/>
@@ -3383,29 +3713,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T3.3</t>
+          <t>T2.5</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>需求评审 PPT 与答辩</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>全体</t>
+          <t>技术可行性验证（云开发原型）</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr"/>
@@ -3419,12 +3749,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T3.4</t>
+          <t>T2.6</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SRS 修订</t>
+          <t>成本与效益测算</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -3433,16 +3763,16 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr"/>
       <c r="O14" s="6" t="inlineStr"/>
@@ -3455,12 +3785,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T4.1</t>
+          <t>T2.7</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>总体设计报告</t>
+          <t>合规与主体资质核查</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -3469,17 +3799,17 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
       <c r="N15" s="6" t="inlineStr"/>
       <c r="O15" s="6" t="inlineStr"/>
       <c r="P15" s="6" t="inlineStr"/>
@@ -3491,31 +3821,31 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T4.2</t>
+          <t>T2.8</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>交互原型与 UI 视觉设计</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>可行性分析报告撰写（GB 8567）</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr"/>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr"/>
@@ -3527,32 +3857,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T4.3</t>
+          <t>T3.1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>数据库与接口设计</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>需求获取与建模（用例/数据流）</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
@@ -3563,33 +3893,33 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T5.1</t>
+          <t>T3.2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>详细设计报告</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>需求规格说明书 SRS</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
@@ -3599,12 +3929,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T3.3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>设计评审 PPT（翻转 PPT1）</t>
+          <t>需求评审 PPT 与答辩</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3620,11 +3950,11 @@
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
@@ -3635,12 +3965,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T5.3</t>
+          <t>T3.4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>设计修订与接口冻结</t>
+          <t>SRS 修订</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3658,9 +3988,9 @@
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr"/>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
@@ -3671,21 +4001,21 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>T6.1</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>框架搭建与登录认证</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>总体设计报告</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
@@ -3694,9 +4024,9 @@
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr"/>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
@@ -3707,12 +4037,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T6.2</t>
+          <t>T4.2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>快递代取模块开发</t>
+          <t>交互原型与 UI 视觉设计</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -3729,11 +4059,11 @@
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
@@ -3743,17 +4073,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T6.3</t>
+          <t>T4.3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>二手教材模块开发</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>数据库与接口设计</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -3767,9 +4097,9 @@
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
@@ -3779,21 +4109,21 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T6.4</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>云函数与数据库实现</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>详细设计报告</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
@@ -3803,9 +4133,9 @@
       <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
-      <c r="O24" s="8" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" s="10" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
@@ -3815,21 +4145,21 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>T6.5</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>积分账本与风控规则</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>设计评审 PPT（翻转 PPT1）</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>全体</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
@@ -3840,8 +4170,8 @@
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
-      <c r="O25" s="8" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
@@ -3851,12 +4181,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T6.6</t>
+          <t>T5.3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>信用评价与申诉模块</t>
+          <t>设计修订与接口冻结</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -3877,7 +4207,7 @@
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
-      <c r="O26" s="8" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
@@ -3887,12 +4217,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>T6.7</t>
+          <t>T6.1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>地图与消息推送对接</t>
+          <t>框架搭建与登录认证</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -3901,7 +4231,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
@@ -3911,10 +4241,10 @@
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr"/>
-      <c r="O27" s="10" t="inlineStr"/>
-      <c r="P27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
@@ -3923,21 +4253,21 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T6.8</t>
+          <t>T6.2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>集成联调与代码清单（翻转PPT2）</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>全体</t>
+          <t>快递代取模块开发</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr"/>
@@ -3948,9 +4278,9 @@
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
@@ -3959,12 +4289,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T6.3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>测试用例设计</t>
+          <t>二手教材模块开发</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -3973,7 +4303,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr"/>
@@ -3984,9 +4314,9 @@
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="10" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
@@ -3995,21 +4325,21 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T6.4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>功能与边界测试</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>云函数与数据库实现</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr"/>
@@ -4019,11 +4349,11 @@
       <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr"/>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="10" t="inlineStr"/>
-      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="8" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="inlineStr"/>
@@ -4031,12 +4361,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T7.3</t>
+          <t>T6.5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>并发与积分一致性测试</t>
+          <t>积分账本与风控规则</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -4045,7 +4375,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr"/>
@@ -4056,10 +4386,10 @@
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr"/>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="8" t="inlineStr"/>
-      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
@@ -4067,17 +4397,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T7.4</t>
+          <t>T6.6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>系统测试报告</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>信用评价与申诉模块</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -4092,10 +4422,10 @@
       <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
-      <c r="N32" s="6" t="inlineStr"/>
-      <c r="O32" s="6" t="inlineStr"/>
-      <c r="P32" s="10" t="inlineStr"/>
-      <c r="Q32" s="10" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr"/>
+      <c r="O32" s="8" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
@@ -4103,17 +4433,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T7.5</t>
+          <t>T6.7</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>测试评审与缺陷修复</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>地图与消息推送对接</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -4129,9 +4459,9 @@
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr"/>
-      <c r="O33" s="6" t="inlineStr"/>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" s="10" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
@@ -4139,21 +4469,21 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T8.1</t>
+          <t>T6.8</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>性能与体验优化</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>集成联调与代码清单（翻转PPT2）</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>全体</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr"/>
@@ -4165,22 +4495,22 @@
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr"/>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="8" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>T8.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>单校区试运行与用户反馈</t>
+          <t>测试用例设计</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -4189,7 +4519,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr"/>
@@ -4201,22 +4531,22 @@
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr"/>
-      <c r="O35" s="6" t="inlineStr"/>
-      <c r="P35" s="6" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" s="10" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T8.3</t>
+          <t>T7.2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>用户使用手册编写</t>
+          <t>功能与边界测试</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -4225,7 +4555,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr"/>
@@ -4238,21 +4568,21 @@
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr"/>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="10" t="inlineStr"/>
+      <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>T9.1</t>
+          <t>T7.3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>项目总结报告</t>
+          <t>并发与积分一致性测试</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -4261,7 +4591,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr"/>
@@ -4274,30 +4604,30 @@
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr"/>
       <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="P37" s="8" t="inlineStr"/>
+      <c r="Q37" s="8" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="8" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>T9.2</t>
+          <t>T7.4</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>总评审 PPT 与答辩</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>全体</t>
+          <t>系统测试报告</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr"/>
@@ -4310,26 +4640,26 @@
       <c r="M38" s="6" t="inlineStr"/>
       <c r="N38" s="6" t="inlineStr"/>
       <c r="O38" s="6" t="inlineStr"/>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="10" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>T9.3</t>
+          <t>T7.5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>课程作业评审与资料归档</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>全体</t>
+          <t>测试评审与缺陷修复</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -4347,112 +4677,328 @@
       <c r="N39" s="6" t="inlineStr"/>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>T8.1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>性能与体验优化</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="6" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="8" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>T8.2</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>单校区试运行与用户反馈</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="10" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>T8.3</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>用户使用手册编写</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" s="6" t="inlineStr"/>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="10" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>T9.1</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>项目总结报告</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="8" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>T9.2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>总评审 PPT 与答辩</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
+      <c r="O44" s="6" t="inlineStr"/>
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>T9.3</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>课程作业评审与资料归档</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr">
+      <c r="M46" s="12" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="N40" s="12" t="inlineStr">
+      <c r="N46" s="12" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="O40" s="12" t="inlineStr">
+      <c r="O46" s="12" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="P46" s="12" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="Q40" s="12" t="inlineStr">
+      <c r="Q46" s="12" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="S40" s="12" t="inlineStr">
+      <c r="S46" s="12" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="T40" s="12" t="inlineStr">
+      <c r="T46" s="12" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="13" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>罗嘉昊</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>李雨鑫</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="16" t="inlineStr">
+    <row r="49">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
@@ -4469,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4702,7 +5248,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>T2.1 需求调研与竞品分析</t>
+          <t>T2.1 调研方案与问卷设计</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4714,10 +5260,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -4728,12 +5274,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>T2.2 可行性分析报告</t>
+          <t>T2.2 问卷发放与回收（≥200 份）</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -4743,18 +5289,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3.35</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>T3.1</t>
+          <t>T2.3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>T3.1 需求获取与建模（用例/数据流）</t>
+          <t>T2.3 竞品分析与群内供需观察</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4763,76 +5309,76 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>T3.2</t>
+          <t>T2.4</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>T3.2 需求规格说明书 SRS</t>
+          <t>T2.4 调研数据整理与统计</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>T3.3</t>
+          <t>T2.5</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>T3.3 需求评审 PPT 与答辩</t>
+          <t>T2.5 技术可行性验证（云开发原型）</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>T3.4</t>
+          <t>T2.6</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>T3.4 SRS 修订</t>
+          <t>T2.6 成本与效益测算</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4841,24 +5387,24 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>T4.1</t>
+          <t>T2.7</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>T4.1 总体设计报告</t>
+          <t>T2.7 合规与主体资质核查</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4867,102 +5413,102 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>T4.2</t>
+          <t>T2.8</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>T4.2 交互原型与 UI 视觉设计</t>
+          <t>T2.8 可行性分析报告撰写（GB 8567）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>T4.3</t>
+          <t>T3.1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>T4.3 数据库与接口设计</t>
+          <t>T3.1 需求获取与建模（用例/数据流）</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>T5.1</t>
+          <t>T3.2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>T5.1 详细设计报告</t>
+          <t>T3.2 需求规格说明书 SRS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>T5.2</t>
+          <t>T3.3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>T5.2 设计评审 PPT（翻转 PPT1）</t>
+          <t>T3.3 需求评审 PPT 与答辩</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4971,10 +5517,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1.5</v>
@@ -4983,12 +5529,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>T5.3</t>
+          <t>T3.4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>T5.3 设计修订与接口冻结</t>
+          <t>T3.4 SRS 修订</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4997,7 +5543,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
@@ -5009,38 +5555,38 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>T6.1</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>T6.1 框架搭建与登录认证</t>
+          <t>T4.1 总体设计报告</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T6.2</t>
+          <t>T4.2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>T6.2 快递代取模块开发</t>
+          <t>T4.2 交互原型与 UI 视觉设计</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5049,10 +5595,10 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>2.5</v>
@@ -5061,21 +5607,21 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T6.3</t>
+          <t>T4.3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>T6.3 二手教材模块开发</t>
+          <t>T4.3 数据库与接口设计</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>2</v>
@@ -5087,17 +5633,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T6.4</t>
+          <t>T5.1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>T6.4 云函数与数据库实现</t>
+          <t>T5.1 详细设计报告</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -5107,44 +5653,44 @@
         <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>T6.5</t>
+          <t>T5.2</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>T6.5 积分账本与风控规则</t>
+          <t>T5.2 设计评审 PPT（翻转 PPT1）</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>T6.6</t>
+          <t>T5.3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>T6.6 信用评价与申诉模块</t>
+          <t>T5.3 设计修订与接口冻结</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5156,7 +5702,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
@@ -5165,12 +5711,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>T6.7</t>
+          <t>T6.1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>T6.7 地图与消息推送对接</t>
+          <t>T6.1 框架搭建与登录认证</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5179,50 +5725,50 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>T6.8</t>
+          <t>T6.2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>T6.8 集成联调与代码清单（翻转PPT2）</t>
+          <t>T6.2 快递代取模块开发</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>T7.1</t>
+          <t>T6.3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>T7.1 测试用例设计</t>
+          <t>T6.3 二手教材模块开发</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5231,50 +5777,50 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>T7.2</t>
+          <t>T6.4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>T7.2 功能与边界测试</t>
+          <t>T6.4 云函数与数据库实现</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>T7.3</t>
+          <t>T6.5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>T7.3 并发与积分一致性测试</t>
+          <t>T6.5 积分账本与风控规则</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5283,33 +5829,33 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T7.4</t>
+          <t>T6.6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>T7.4 系统测试报告</t>
+          <t>T6.6 信用评价与申诉模块</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>2</v>
@@ -5321,24 +5867,24 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>T7.5</t>
+          <t>T6.7</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>T7.5 测试评审与缺陷修复</t>
+          <t>T6.7 地图与消息推送对接</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>1</v>
@@ -5347,38 +5893,38 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>T8.1</t>
+          <t>T6.8</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>T8.1 性能与体验优化</t>
+          <t>T6.8 集成联调与代码清单（翻转PPT2）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>T8.2</t>
+          <t>T7.1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>T8.2 单校区试运行与用户反馈</t>
+          <t>T7.1 测试用例设计</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5387,24 +5933,24 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>T8.3</t>
+          <t>T7.2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>T8.3 用户使用手册编写</t>
+          <t>T7.2 功能与边界测试</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -5413,24 +5959,24 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>T9.1</t>
+          <t>T7.3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>T9.1 项目总结报告</t>
+          <t>T7.3 并发与积分一致性测试</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5439,64 +5985,220 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>T9.2</t>
+          <t>T7.4</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>T9.2 总评审 PPT 与答辩</t>
+          <t>T7.4 系统测试报告</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>T9.3</t>
+          <t>T7.5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>T9.3 课程作业评审与资料归档</t>
+          <t>T7.5 测试评审与缺陷修复</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>T8.1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>T8.1 性能与体验优化</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>T8.2</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>T8.2 单校区试运行与用户反馈</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>T8.3</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>T8.3 用户使用手册编写</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>T9.1</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>T9.1 项目总结报告</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>T9.2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>T9.2 总评审 PPT 与答辩</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>T9.3</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>T9.3 课程作业评审与资料归档</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5648,10 +6350,10 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1.87</v>
@@ -5709,10 +6411,10 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1.62</v>
@@ -5770,10 +6472,10 @@
         <v>1.42</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="G4" s="18" t="n">
         <v>3.49</v>

--- a/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
+++ b/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>调研方案与问卷设计</t>
+          <t>① 复查系统规模和目标</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>调研方案、问卷与访谈提纲</t>
+          <t>系统规模与目标复查清单</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>问卷发放与回收（≥200 份）</t>
+          <t>② 研究现有（正在使用）的系统</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>T2.1</t>
+          <t>T1.4</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>问卷原始数据</t>
+          <t>现有系统分析：问卷、竞品对比表、群内观察记录</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>竞品分析与群内供需观察</t>
+          <t>③ 导出新系统的高层逻辑模型</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>竞品对比表、群内观察记录</t>
+          <t>高层数据流图、系统上下文图</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>调研数据整理与统计</t>
+          <t>④ 进一步定义问题</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>T2.2</t>
+          <t>T2.2, T2.3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>调研数据小结</t>
+          <t>问题定义与约束清单</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>技术可行性验证（云开发原型）</t>
+          <t>⑤ 导出和评价供选择的解法</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1394,36 +1394,36 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>T1.4</t>
+          <t>T2.4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>技术验证结论与原型截图</t>
+          <t>方案对比表（三类可选方案）</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>成本与效益测算</t>
+          <t>⑥ 推荐行动方针</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>T1.4</t>
+          <t>T2.5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>成本测算表、收益/投资比测算</t>
+          <t>推荐方案与理由说明</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>合规与主体资质核查</t>
+          <t>⑦ 草拟开发计划书</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1504,11 +1504,11 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>T1.4</t>
+          <t>T2.6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>合规核查记录、资质路径结论</t>
+          <t>开发计划草案（范围/进度/资源粗估）</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>可行性分析报告撰写（GB 8567）</t>
+          <t>⑧ 编写可行性研究报告并提交审查</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>T2.4</t>
+          <t>T2.5, T2.7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3574,21 +3574,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>调研方案与问卷设计</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>① 复查系统规模和目标</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>问卷发放与回收（≥200 份）</t>
+          <t>② 研究现有（正在使用）的系统</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>竞品分析与群内供需观察</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>李雨鑫</t>
+          <t>③ 导出新系统的高层逻辑模型</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -3660,8 +3660,8 @@
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>调研数据整理与统计</t>
+          <t>④ 进一步定义问题</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -3696,7 +3696,7 @@
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr"/>
       <c r="I12" s="10" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="6" t="inlineStr"/>
@@ -3718,22 +3718,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>技术可行性验证（云开发原型）</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>罗嘉昊</t>
+          <t>⑤ 导出和评价供选择的解法</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>成本与效益测算</t>
+          <t>⑥ 推荐行动方针</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -3763,12 +3763,12 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>合规与主体资质核查</t>
+          <t>⑦ 草拟开发计划书</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -3799,12 +3799,12 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>可行性分析报告撰写（GB 8567）</t>
+          <t>⑧ 编写可行性研究报告并提交审查</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
@@ -5248,12 +5248,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>T2.1 调研方案与问卷设计</t>
+          <t>T2.1 ① 复查系统规模和目标</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -5263,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>T2.2 问卷发放与回收（≥200 份）</t>
+          <t>T2.2 ② 研究现有（正在使用）的系统</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5286,10 +5286,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5300,19 +5300,19 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>T2.3 竞品分析与群内供需观察</t>
+          <t>T2.3 ③ 导出新系统的高层逻辑模型</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>李雨鑫</t>
+          <t>罗嘉昊</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.75</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>T2.4 调研数据整理与统计</t>
+          <t>T2.4 ④ 进一步定义问题</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.5</v>
@@ -5352,22 +5352,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>T2.5 技术可行性验证（云开发原型）</t>
+          <t>T2.5 ⑤ 导出和评价供选择的解法</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>罗嘉昊</t>
+          <t>李雨鑫</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>T2.6 成本与效益测算</t>
+          <t>T2.6 ⑥ 推荐行动方针</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>T2.7 合规与主体资质核查</t>
+          <t>T2.7 ⑦ 草拟开发计划书</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>T2.8 可行性分析报告撰写（GB 8567）</t>
+          <t>T2.8 ⑧ 编写可行性研究报告并提交审查</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="17">
@@ -6350,10 +6350,10 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.29</v>
+        <v>1.87</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1.87</v>
@@ -6411,10 +6411,10 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1.62</v>
@@ -6472,10 +6472,10 @@
         <v>1.42</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>3.92</v>
+        <v>3.12</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="G4" s="18" t="n">
         <v>3.49</v>

--- a/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
+++ b/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>工期(人天)</t>
+          <t>工期(人时)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.85</v>
+        <v>6.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.65</v>
+        <v>13.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>工期(人天)</t>
+          <t>工期(人时)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr"/>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr"/>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.85</v>
+        <v>6.8</v>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1.65</v>
+        <v>13.2</v>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr"/>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr"/>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr"/>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr"/>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr"/>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr"/>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr"/>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr"/>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>工期(人天)</t>
+          <t>工期(人时)</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -5133,7 +5133,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -5159,7 +5159,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -5185,7 +5185,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -5211,7 +5211,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5263,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -5315,7 +5315,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -5341,7 +5341,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -5367,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -5393,7 +5393,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -5419,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.85</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17">
@@ -5471,7 +5471,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -5497,7 +5497,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -5523,7 +5523,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -5549,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -5575,7 +5575,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -5601,7 +5601,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -5627,7 +5627,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -5653,7 +5653,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1.65</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="25">
@@ -5679,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -5705,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -5731,7 +5731,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -5757,7 +5757,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -5783,7 +5783,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -5809,7 +5809,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -5835,7 +5835,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -5861,7 +5861,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -5887,7 +5887,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -5913,7 +5913,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -5939,7 +5939,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -5965,7 +5965,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -5991,7 +5991,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -6017,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -6095,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -6147,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -6173,7 +6173,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -6199,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>合计(人天)</t>
+          <t>合计(人时)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>平均(人天/周)</t>
+          <t>平均(人时/周)</t>
         </is>
       </c>
     </row>
@@ -6341,58 +6341,58 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.67</v>
+        <v>13.33</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.92</v>
+        <v>7.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.87</v>
+        <v>14.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.47</v>
+        <v>19.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.87</v>
+        <v>14.95</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.87</v>
+        <v>14.95</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.49</v>
+        <v>19.95</v>
       </c>
       <c r="J2" s="17" t="n">
-        <v>3.33</v>
+        <v>26.62</v>
       </c>
       <c r="K2" s="17" t="n">
-        <v>5.58</v>
+        <v>44.62</v>
       </c>
       <c r="L2" s="17" t="n">
-        <v>3.08</v>
+        <v>24.62</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.24</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.99</v>
+        <v>15.95</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.74</v>
+        <v>13.95</v>
       </c>
       <c r="P2" s="17" t="n">
-        <v>2.99</v>
+        <v>23.95</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.74</v>
+        <v>5.95</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>34.1</v>
+        <v>272.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.13</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="3">
@@ -6402,58 +6402,58 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.62</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.46</v>
+        <v>19.67</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.83</v>
+        <v>6.67</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.13</v>
+        <v>17.07</v>
       </c>
       <c r="K3" s="17" t="n">
-        <v>4.3</v>
+        <v>34.4</v>
       </c>
       <c r="L3" s="17" t="n">
-        <v>4.3</v>
+        <v>34.4</v>
       </c>
       <c r="M3" s="17" t="n">
-        <v>2.75</v>
+        <v>22</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="O3" s="17" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>27.9</v>
+        <v>223.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.74</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="4">
@@ -6463,64 +6463,64 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>2.42</v>
+        <v>19.33</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>1.42</v>
+        <v>11.33</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>3.12</v>
+        <v>24.95</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>3.72</v>
+        <v>29.75</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>3.49</v>
+        <v>27.95</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>4.33</v>
+        <v>34.62</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>3.33</v>
+        <v>26.62</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>5.46</v>
+        <v>43.68</v>
       </c>
       <c r="K4" s="18" t="n">
-        <v>9.880000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="L4" s="18" t="n">
-        <v>7.38</v>
+        <v>59.02</v>
       </c>
       <c r="M4" s="18" t="n">
-        <v>3.99</v>
+        <v>31.95</v>
       </c>
       <c r="N4" s="18" t="n">
-        <v>3.24</v>
+        <v>25.95</v>
       </c>
       <c r="O4" s="18" t="n">
-        <v>4.74</v>
+        <v>37.95</v>
       </c>
       <c r="P4" s="18" t="n">
-        <v>3.74</v>
+        <v>29.95</v>
       </c>
       <c r="Q4" s="18" t="n">
-        <v>1.24</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>62</v>
+        <v>496</v>
       </c>
       <c r="S4" t="n">
-        <v>3.88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>基准产能：每人每周 2.5 人天；总产能 80.0 人天；总工作量 62.00 人天；利用率 77.5%</t>
+          <t>基准产能：每人每周 20 人时；总产能 640.0 人时；总工作量 496.00 人时；利用率 77.5%</t>
         </is>
       </c>
     </row>
@@ -6534,14 +6534,14 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>峰值周：W10（合计 9.88 人天）—— 为集成联调与内测截止周</t>
+          <t>峰值周：W10（合计 79.02 人时）—— 为集成联调与内测截止周</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>高于个人周产能 2.5 人天的工作量以粗体标注</t>
+          <t>高于个人周产能 20 人时的工作量以粗体标注</t>
         </is>
       </c>
     </row>

--- a/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
+++ b/design/SE2026-G22-校园互助平台-任务计划与甘特图.xlsx
@@ -382,6 +382,36 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="742950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
@@ -3178,6 +3208,7 @@
   </sheetData>
   <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
